--- a/data/export/2026-10-22-operations.xlsx
+++ b/data/export/2026-10-22-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +912,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +936,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1032,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1071,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1082,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1115,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1152,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1176,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1196,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1272,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1322,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1388,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1438,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1504,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1554,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1567,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1615,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1634,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1670,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1731,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1750,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1786,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1847,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1866,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1902,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1963,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1982,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,7 +2007,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2002,35 +2018,35 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2079,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2098,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2134,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2195,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2214,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2250,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2311,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2330,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2355,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2431,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2450,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2475,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2486,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2499,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2547,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2566,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,25 +2602,25 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2610,41 +2630,37 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2652,7 +2668,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2676,17 +2692,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2696,45 +2712,41 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2772,7 +2784,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2786,7 +2798,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2822,35 +2834,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2888,7 +2900,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2902,7 +2914,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2938,35 +2950,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2999,12 +3011,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3018,7 +3030,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3054,7 +3066,3731 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>1/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>1/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-operations.xlsx
+++ b/data/export/2026-10-22-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD54"/>
+  <dimension ref="A1:AD79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -912,7 +912,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -999,32 +999,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1032,7 +1036,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1056,17 +1060,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1076,13 +1080,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1145,12 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1152,7 +1160,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1191,14 +1199,14 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>92.0</t>
@@ -1206,7 +1214,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1239,32 +1247,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1272,7 +1284,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1296,33 +1308,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1355,32 +1371,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1388,7 +1408,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1412,33 +1432,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1528,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1543,7 +1567,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1554,7 +1578,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1644,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1659,7 +1683,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1670,7 +1694,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1703,32 +1727,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1736,7 +1764,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1760,33 +1788,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1884,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1902,7 +1934,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1968,7 +2000,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2018,7 +2050,7 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2116,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2134,7 +2166,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2232,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2250,7 +2282,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2348,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2365,12 +2397,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2383,22 +2415,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2436,7 +2468,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2450,7 +2482,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2486,35 +2518,35 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2547,12 +2579,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2566,7 +2598,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2591,46 +2623,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2663,12 +2699,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2682,7 +2718,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2707,46 +2743,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2779,12 +2819,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2798,7 +2838,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2834,35 +2874,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2895,12 +2935,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2914,7 +2954,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2939,46 +2979,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3011,12 +3055,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3030,7 +3074,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3055,46 +3099,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3127,12 +3175,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3146,7 +3194,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3171,7 +3219,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3182,35 +3230,35 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3243,12 +3291,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3262,7 +3310,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3287,7 +3335,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3298,35 +3346,35 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3359,12 +3407,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3378,7 +3426,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3403,18 +3451,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3427,22 +3479,22 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3475,12 +3527,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3494,7 +3546,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3519,7 +3571,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3530,7 +3582,7 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3543,60 +3595,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3610,7 +3666,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3620,33 +3676,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3659,60 +3719,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3726,7 +3790,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3736,17 +3800,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3756,13 +3820,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3843,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3785,7 +3853,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3823,12 +3891,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3842,7 +3910,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3878,7 +3946,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3891,32 +3959,32 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3939,12 +4007,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3952,13 +4020,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3994,7 +4078,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4091,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4017,7 +4101,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4055,12 +4139,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4074,7 +4158,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4110,7 +4194,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4207,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4133,7 +4217,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4171,12 +4255,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4190,7 +4274,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4226,7 +4310,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4323,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4249,7 +4333,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4287,12 +4371,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4306,7 +4390,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4342,7 +4426,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4439,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4365,7 +4449,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4403,12 +4487,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4422,7 +4506,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4458,7 +4542,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4555,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4481,7 +4565,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4524,7 +4608,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4538,7 +4622,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4574,7 +4658,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4671,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4597,7 +4681,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4635,12 +4719,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4654,7 +4738,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4690,7 +4774,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4703,22 +4787,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4751,12 +4835,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4770,7 +4854,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4806,77 +4890,73 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4890,7 +4970,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4900,65 +4980,61 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>1/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4991,12 +5067,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5010,7 +5086,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5046,35 +5122,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5107,12 +5183,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5126,7 +5202,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5162,35 +5238,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5223,12 +5299,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5242,7 +5318,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5278,35 +5354,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5339,12 +5415,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5358,7 +5434,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5394,35 +5470,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5455,12 +5531,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5474,7 +5550,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5510,35 +5586,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5571,12 +5647,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5590,7 +5666,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5626,35 +5702,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5687,12 +5763,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5706,7 +5782,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5742,35 +5818,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5803,12 +5879,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5822,7 +5898,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5858,35 +5934,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5919,12 +5995,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5938,7 +6014,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5974,35 +6050,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A62773D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6035,12 +6111,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6054,7 +6130,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6090,35 +6166,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6151,12 +6227,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6170,7 +6246,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6206,35 +6282,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6267,12 +6343,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6286,7 +6362,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6322,35 +6398,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6383,12 +6459,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6402,7 +6478,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6438,35 +6514,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6504,7 +6580,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6518,7 +6594,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6554,35 +6630,35 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6615,12 +6691,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6634,7 +6710,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6670,35 +6746,35 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6736,7 +6812,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6750,7 +6826,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6785,12 +6861,2948 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/16</t>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-operations.xlsx
+++ b/data/export/2026-10-22-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD79"/>
+  <dimension ref="A1:AD84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1611,32 +1611,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1644,7 +1648,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1668,17 +1672,17 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1688,13 +1692,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1745,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1764,7 +1772,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1813,12 +1821,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1892,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2000,7 +2008,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2039,7 +2047,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2116,7 +2124,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2232,7 +2240,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2348,7 +2356,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2468,7 +2476,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2584,7 +2592,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2704,7 +2712,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2758,7 +2766,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2948,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2994,7 +3002,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3068,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3114,7 +3122,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3188,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3296,7 +3304,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3340,13 +3348,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3424,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3461,40 +3473,40 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3527,12 +3539,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3546,7 +3558,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3571,7 +3583,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3582,7 +3594,7 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3595,56 +3607,52 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>06:10</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3652,7 +3660,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3676,17 +3684,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3696,17 +3704,13 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3719,24 +3723,24 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>06:26</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3749,24 +3753,24 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3776,7 +3780,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3790,7 +3794,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3815,22 +3819,22 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3843,52 +3847,56 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3896,7 +3904,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3910,7 +3918,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3920,33 +3928,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3959,32 +3971,32 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:36</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4012,7 +4024,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4020,29 +4032,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq27（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:44</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:53</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4067,7 +4063,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4091,7 +4087,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4101,7 +4097,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4111,12 +4107,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4139,12 +4135,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4152,13 +4148,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr"/>
-      <c r="U31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4207,22 +4219,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4255,12 +4267,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4274,7 +4286,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4323,22 +4335,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4371,12 +4383,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4390,7 +4402,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4439,22 +4451,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4487,12 +4499,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4555,22 +4567,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4603,12 +4615,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4622,7 +4634,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4671,22 +4683,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4724,7 +4736,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4787,7 +4799,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4797,7 +4809,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4835,12 +4847,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4854,7 +4866,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4903,7 +4915,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4913,7 +4925,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4951,12 +4963,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4970,7 +4982,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5019,22 +5031,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5067,12 +5079,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5135,22 +5147,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5183,12 +5195,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5202,7 +5214,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5251,22 +5263,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5299,7 +5311,7 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5318,7 +5330,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5367,22 +5379,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5415,12 +5427,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5483,22 +5495,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5531,12 +5543,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5550,7 +5562,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5599,22 +5611,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5647,12 +5659,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5715,22 +5727,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5768,7 +5780,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5782,7 +5794,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5831,22 +5843,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5879,12 +5891,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5947,22 +5959,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5995,12 +6007,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6014,7 +6026,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6063,22 +6075,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A62773D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6111,12 +6123,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6179,22 +6191,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A62773D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6232,7 +6244,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6246,7 +6258,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6295,22 +6307,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6343,12 +6355,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6411,7 +6423,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6421,7 +6433,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6459,12 +6471,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6478,7 +6490,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6527,22 +6539,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6580,7 +6592,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6643,22 +6655,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6691,12 +6703,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6710,7 +6722,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6759,22 +6771,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6807,12 +6819,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6826,7 +6838,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6851,22 +6863,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6879,22 +6887,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6932,7 +6940,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6946,7 +6954,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6976,41 +6984,45 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7048,7 +7060,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7062,7 +7074,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7098,35 +7110,35 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7164,7 +7176,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7178,7 +7190,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7208,83 +7220,83 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7298,7 +7310,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7308,17 +7320,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7328,17 +7340,13 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7359,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7361,7 +7369,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7404,7 +7412,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7418,7 +7426,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7467,7 +7475,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7477,7 +7485,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7515,12 +7523,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7534,7 +7542,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7559,7 +7567,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7583,7 +7591,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7593,7 +7601,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7613,7 +7621,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7625,12 +7633,12 @@
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -7640,7 +7648,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7654,7 +7662,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7707,7 +7715,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7717,7 +7725,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7755,12 +7763,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7774,7 +7782,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7799,7 +7807,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7823,64 +7831,60 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7894,7 +7898,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7904,17 +7908,17 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7924,17 +7928,13 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -7947,52 +7947,56 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8014,7 +8018,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8024,33 +8028,37 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8063,22 +8071,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8111,12 +8119,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8130,7 +8138,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8179,60 +8187,64 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8246,7 +8258,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8256,33 +8268,37 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8311,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8305,7 +8321,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8343,12 +8359,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8362,7 +8378,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8411,7 +8427,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8421,7 +8437,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8459,12 +8475,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8478,7 +8494,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8503,7 +8519,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8527,7 +8543,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8537,7 +8553,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8575,12 +8591,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8594,7 +8610,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8643,22 +8659,22 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8691,12 +8707,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8710,7 +8726,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8759,22 +8775,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8807,12 +8823,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8826,7 +8842,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8875,22 +8891,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:04</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8923,7 +8939,7 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8942,7 +8958,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8967,7 +8983,7 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -8991,22 +9007,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -9039,12 +9055,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9058,7 +9074,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9107,7 +9123,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9117,7 +9133,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9160,7 +9176,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9174,7 +9190,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9199,22 +9215,18 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9239,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9237,7 +9249,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9280,7 +9292,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9294,7 +9306,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9343,22 +9355,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9391,12 +9403,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9410,7 +9422,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9435,7 +9447,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9459,7 +9471,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9469,7 +9481,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9512,7 +9524,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9526,7 +9538,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9579,7 +9591,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9589,7 +9601,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9627,12 +9639,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9646,7 +9658,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9671,7 +9683,7 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
@@ -9695,22 +9707,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9743,12 +9755,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9762,47 +9774,631 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="W79" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X79" s="2" t="inlineStr">
+      <c r="X82" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y79" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z79" s="2" t="inlineStr">
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
+      <c r="AA82" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC79" s="2" t="inlineStr">
+      <c r="AC83" s="2" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="AD79" s="2" t="inlineStr">
+      <c r="AD83" s="2" t="inlineStr">
         <is>
           <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-operations.xlsx
+++ b/data/export/2026-10-22-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD84"/>
+  <dimension ref="A1:AD104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -720,13 +720,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -792,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -912,7 +916,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -951,17 +955,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1036,7 +1040,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1075,22 +1079,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1164,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1284,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1408,7 +1412,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1462,7 +1466,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1532,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1648,7 +1652,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1702,7 +1706,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1776,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1859,32 +1863,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1892,7 +1900,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1916,33 +1924,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1975,32 +1987,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2008,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2032,17 +2048,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2052,13 +2068,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2091,32 +2111,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2124,7 +2148,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2148,33 +2172,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2207,32 +2235,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2240,7 +2272,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2264,33 +2296,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2323,32 +2359,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2356,7 +2396,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2380,32 +2420,32 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2476,7 +2516,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2559,32 +2599,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2592,7 +2636,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2616,37 +2660,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2756,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2832,7 +2876,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2948,7 +2992,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3068,7 +3112,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3122,7 +3166,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3232,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3304,7 +3348,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3358,7 +3402,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3468,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3491,22 +3535,22 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3544,7 +3588,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3558,7 +3602,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3583,46 +3627,50 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3655,12 +3703,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3674,7 +3722,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3699,88 +3747,88 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3794,7 +3842,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3804,17 +3852,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3829,82 +3877,78 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3918,7 +3962,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3928,17 +3972,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3953,40 +3997,40 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4019,12 +4063,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4038,7 +4082,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4063,56 +4107,60 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4135,12 +4183,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4148,29 +4196,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>物理seq27（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>07:44</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>07:53</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4195,18 +4227,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4255,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4229,7 +4265,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4267,12 +4303,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4286,7 +4322,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4311,7 +4347,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4335,7 +4371,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4345,7 +4381,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4355,32 +4391,36 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4388,7 +4428,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4402,7 +4442,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4412,33 +4452,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4495,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4461,7 +4505,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4471,40 +4515,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4518,7 +4566,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4528,33 +4576,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4619,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4577,7 +4629,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4615,12 +4667,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4634,7 +4686,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4659,7 +4711,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4683,7 +4735,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4693,7 +4745,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4703,12 +4755,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4731,12 +4783,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4744,13 +4796,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4775,7 +4843,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4799,60 +4867,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4866,7 +4938,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4876,33 +4948,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4991,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4925,7 +5001,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4935,40 +5011,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4982,7 +5062,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4992,33 +5072,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5031,60 +5115,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5098,7 +5186,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5108,33 +5196,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5147,22 +5239,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5195,12 +5287,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5214,7 +5306,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5239,7 +5331,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5263,22 +5355,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5311,12 +5403,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5330,7 +5422,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5355,7 +5447,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5379,22 +5471,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5427,12 +5519,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5446,7 +5538,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5495,7 +5587,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5505,7 +5597,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5543,12 +5635,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5562,7 +5654,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5611,22 +5703,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5659,12 +5751,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5678,7 +5770,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5727,22 +5819,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5775,12 +5867,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5794,7 +5886,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5843,32 +5935,32 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq41推进至seq49，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5891,12 +5983,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5904,13 +5996,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>沪南路华夏西路</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq21映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5959,22 +6063,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6007,12 +6111,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6026,7 +6130,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6075,22 +6179,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6123,12 +6227,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6142,7 +6246,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6191,22 +6295,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A62773D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6239,12 +6343,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6258,7 +6362,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6307,22 +6411,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6355,12 +6459,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6374,7 +6478,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6423,22 +6527,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6471,12 +6575,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6490,7 +6594,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6539,7 +6643,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6549,7 +6653,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6587,12 +6691,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6606,7 +6710,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6655,7 +6759,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6665,7 +6769,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6703,12 +6807,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6722,7 +6826,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6771,7 +6875,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62773D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6781,7 +6885,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6819,12 +6923,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6838,7 +6942,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6887,7 +6991,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6897,7 +7001,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6940,7 +7044,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6954,7 +7058,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6979,22 +7083,18 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7107,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7017,7 +7117,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7055,12 +7155,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7074,7 +7174,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7099,7 +7199,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7123,7 +7223,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7133,7 +7233,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7176,7 +7276,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7190,7 +7290,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7215,22 +7315,18 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7339,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7253,7 +7349,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7296,7 +7392,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7310,7 +7406,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7335,7 +7431,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7353,28 +7449,28 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7407,12 +7503,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7426,7 +7522,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7451,7 +7547,7 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -7462,35 +7558,35 @@
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7528,7 +7624,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7542,7 +7638,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7572,83 +7668,83 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7662,7 +7758,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7672,17 +7768,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7692,45 +7788,41 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7768,7 +7860,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7782,7 +7874,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7812,41 +7904,45 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7879,12 +7975,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7898,7 +7994,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7934,77 +8030,73 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8018,7 +8110,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8028,17 +8120,17 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8048,45 +8140,41 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8119,12 +8207,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8138,7 +8226,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8163,88 +8251,88 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8258,7 +8346,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8268,17 +8356,17 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8293,40 +8381,40 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8364,7 +8452,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8378,7 +8466,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8403,46 +8491,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8475,12 +8567,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8494,7 +8586,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8530,35 +8622,35 @@
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8591,12 +8683,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8610,7 +8702,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8635,7 +8727,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8646,7 +8738,7 @@
       <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8751,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8669,7 +8761,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8707,12 +8799,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8726,7 +8818,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8751,18 +8843,22 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8775,22 +8871,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8823,12 +8919,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8842,7 +8938,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8867,7 +8963,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8891,60 +8987,64 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8958,7 +9058,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8968,33 +9068,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9007,22 +9111,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -9060,7 +9164,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9074,7 +9178,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9099,7 +9203,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9123,7 +9227,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9133,7 +9237,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9171,12 +9275,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9190,7 +9294,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9215,7 +9319,7 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9239,7 +9343,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9249,7 +9353,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9259,40 +9363,44 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9306,7 +9414,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9316,17 +9424,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9336,13 +9444,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9355,7 +9467,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9365,7 +9477,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9403,12 +9515,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9422,7 +9534,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9447,7 +9559,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9471,52 +9583,56 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9524,7 +9640,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9538,7 +9654,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9548,17 +9664,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9573,12 +9689,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9591,22 +9707,22 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9639,12 +9755,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9658,7 +9774,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9707,7 +9823,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9717,7 +9833,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9727,40 +9843,44 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9774,7 +9894,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9784,17 +9904,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9804,13 +9924,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9947,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9833,7 +9957,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9843,40 +9967,44 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9890,7 +10018,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9900,17 +10028,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9925,12 +10053,12 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9943,60 +10071,64 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10010,7 +10142,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10020,33 +10152,37 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB81" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10195,7 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -10069,7 +10205,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10079,40 +10215,44 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10126,7 +10266,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10136,17 +10276,17 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10156,13 +10296,17 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10319,7 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -10185,7 +10329,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10223,12 +10367,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10242,7 +10386,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10267,22 +10411,18 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC83" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10295,60 +10435,64 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10362,43 +10506,2423 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W84" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X84" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y84" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z84" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB84" s="2" t="inlineStr">
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC84" s="2" t="inlineStr"/>
-      <c r="AD84" s="2" t="inlineStr">
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD104" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-operations.xlsx
+++ b/data/export/2026-10-22-operations.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3556,17 +3556,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3928,17 +3928,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5168,17 +5168,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5292,17 +5292,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5416,17 +5416,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6408,17 +6408,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7276,17 +7276,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7524,17 +7524,17 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8268,17 +8268,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8632,17 +8632,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8752,17 +8752,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9244,12 +9244,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10236,17 +10236,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10360,17 +10360,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10732,17 +10732,17 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10980,12 +10980,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
@@ -11281,24 +11281,24 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11405,12 +11405,12 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
@@ -11432,7 +11432,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
@@ -11529,19 +11529,19 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11643,32 +11643,36 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11676,7 +11680,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11700,17 +11704,17 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11720,17 +11724,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11763,32 +11767,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11796,7 +11804,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11820,17 +11828,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11840,17 +11848,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11883,32 +11891,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11916,7 +11928,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11940,17 +11952,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11960,17 +11972,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -12003,32 +12015,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12036,7 +12052,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12060,17 +12076,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12080,12 +12096,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12123,32 +12139,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12156,7 +12176,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12180,17 +12200,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12200,12 +12220,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12276,7 +12296,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12325,12 +12345,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12416,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12440,17 +12460,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12536,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12560,17 +12580,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -12694,7 +12714,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12838,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13160,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13194,7 +13214,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -13264,7 +13284,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13318,7 +13338,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -13442,7 +13462,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -13562,7 +13582,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13652,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13686,7 +13706,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13776,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13800,17 +13820,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -13942,7 +13962,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14032,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14066,7 +14086,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -14190,7 +14210,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -14256,7 +14276,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14322,7 +14342,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14412,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14446,7 +14466,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14652,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14681,7 +14701,7 @@
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
@@ -14756,7 +14776,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14810,7 +14830,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14896,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14920,12 +14940,12 @@
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
@@ -15000,7 +15020,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15054,7 +15074,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -15124,7 +15144,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15168,17 +15188,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15322,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15446,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15516,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15550,7 +15570,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -15616,7 +15636,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15660,17 +15680,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15814,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -15864,7 +15884,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -16042,7 +16062,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16132,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16156,17 +16176,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -16290,7 +16310,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -16616,7 +16636,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16670,7 +16690,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -16736,7 +16756,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16790,7 +16810,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -16910,7 +16930,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -17034,7 +17054,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -17104,7 +17124,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17158,7 +17178,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -17228,7 +17248,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17272,17 +17292,17 @@
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -17352,7 +17372,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17406,7 +17426,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -17530,7 +17550,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -17724,7 +17744,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17778,7 +17798,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -17848,7 +17868,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17902,7 +17922,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17992,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18021,7 +18041,7 @@
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
@@ -18096,7 +18116,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18140,12 +18160,12 @@
       </c>
       <c r="AB143" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
@@ -18220,7 +18240,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18274,7 +18294,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -18344,7 +18364,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18388,17 +18408,17 @@
       </c>
       <c r="AB145" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC145" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -18468,7 +18488,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18522,7 +18542,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -18646,7 +18666,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -18716,7 +18736,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -19014,7 +19034,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -19138,7 +19158,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -19262,7 +19282,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -19518,7 +19538,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -19642,7 +19662,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19732,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19766,7 +19786,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19856,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19885,7 +19905,7 @@
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
@@ -20084,7 +20104,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20128,17 +20148,17 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20228,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20262,7 +20282,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -20386,7 +20406,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -20510,7 +20530,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -20704,7 +20724,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -20758,7 +20778,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -20882,7 +20902,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -20948,7 +20968,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -20992,17 +21012,17 @@
       </c>
       <c r="AB166" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC166" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21146,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21216,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21250,7 +21270,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -21448,7 +21468,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21618,7 +21638,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -21688,7 +21708,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21732,17 +21752,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -21812,7 +21832,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21866,7 +21886,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21956,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21990,7 +22010,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -22060,7 +22080,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22114,7 +22134,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -22184,7 +22204,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22228,17 +22248,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -22308,7 +22328,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22362,7 +22382,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22452,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22556,7 +22576,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22610,7 +22630,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -22730,7 +22750,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22874,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -22924,7 +22944,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22978,7 +22998,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -23102,7 +23122,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -23226,7 +23246,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -23281,12 +23301,12 @@
       <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N185" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O185" s="2" t="inlineStr">
@@ -23296,7 +23316,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23350,7 +23370,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -23393,24 +23413,24 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O186" s="2" t="inlineStr">
@@ -23420,7 +23440,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23469,7 +23489,7 @@
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
@@ -23594,7 +23614,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -23627,32 +23647,36 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N188" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23660,7 +23684,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23684,17 +23708,17 @@
       </c>
       <c r="X188" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z188" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA188" s="2" t="inlineStr">
@@ -23704,12 +23728,12 @@
       </c>
       <c r="AB188" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC188" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AD188" s="2" t="inlineStr">
@@ -23747,32 +23771,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23780,7 +23808,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23804,17 +23832,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23824,17 +23852,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -23867,32 +23895,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -23900,7 +23932,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23924,17 +23956,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23944,13 +23976,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC190" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC190" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -23983,32 +24019,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24016,7 +24056,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24040,17 +24080,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24060,17 +24100,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -24103,32 +24143,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -24136,7 +24180,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24160,17 +24204,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24180,17 +24224,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -24228,7 +24272,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -24256,7 +24300,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24326,7 +24370,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -24359,32 +24403,36 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24392,7 +24440,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24416,17 +24464,17 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA194" s="2" t="inlineStr">
@@ -24436,17 +24484,17 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -24512,7 +24560,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24566,7 +24614,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -24599,12 +24647,12 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -24632,7 +24680,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24640,10 +24688,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R196" s="2" t="inlineStr"/>
-      <c r="S196" s="2" t="inlineStr"/>
-      <c r="T196" s="2" t="inlineStr"/>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="V196" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24752,7 +24816,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24806,7 +24870,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -24872,7 +24936,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24926,7 +24990,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -24992,7 +25056,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25046,7 +25110,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -25112,7 +25176,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25166,7 +25230,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -25232,7 +25296,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25286,7 +25350,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -25352,7 +25416,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25406,7 +25470,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -25472,7 +25536,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25516,12 +25580,12 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
@@ -25592,7 +25656,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25636,17 +25700,17 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -25890,7 +25954,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -26076,7 +26140,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26125,12 +26189,12 @@
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -26200,7 +26264,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26249,7 +26313,7 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
@@ -26374,7 +26438,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -26684,7 +26748,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26728,17 +26792,17 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -26862,7 +26926,7 @@
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -26986,7 +27050,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -27230,7 +27294,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27418,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -27424,7 +27488,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27468,17 +27532,17 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -27548,7 +27612,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27592,17 +27656,17 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -27726,7 +27790,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -27846,7 +27910,7 @@
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -28156,7 +28220,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28205,7 +28269,7 @@
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
@@ -28396,7 +28460,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28445,12 +28509,12 @@
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -28644,7 +28708,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28688,17 +28752,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -28818,7 +28882,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -29054,7 +29118,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -29302,7 +29366,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -29426,7 +29490,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -29492,7 +29556,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29536,17 +29600,17 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -29794,7 +29858,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -29860,7 +29924,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -29921,7 +29985,7 @@
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
@@ -30240,7 +30304,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30296,17 +30360,17 @@
       </c>
       <c r="AB242" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC242" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -30430,7 +30494,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -30678,7 +30742,7 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -30802,7 +30866,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -30926,7 +30990,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -31174,7 +31238,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -31546,7 +31610,7 @@
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -31794,7 +31858,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -31918,7 +31982,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -32042,7 +32106,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -32290,7 +32354,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -32608,7 +32672,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32652,17 +32716,17 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -32786,7 +32850,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -33034,7 +33098,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -33104,7 +33168,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33153,12 +33217,12 @@
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -33282,7 +33346,7 @@
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -33406,7 +33470,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -33476,7 +33540,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33525,7 +33589,7 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
@@ -33650,7 +33714,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -33774,7 +33838,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -33844,7 +33908,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -33893,7 +33957,7 @@
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD271" s="2" t="inlineStr">
@@ -33968,7 +34032,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34012,17 +34076,17 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -34266,7 +34330,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -34336,7 +34400,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34380,17 +34444,17 @@
       </c>
       <c r="AB275" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -34708,7 +34772,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34752,17 +34816,17 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -34886,7 +34950,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -35134,7 +35198,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -35258,7 +35322,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -35328,7 +35392,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35377,12 +35441,12 @@
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -35506,7 +35570,7 @@
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -35576,7 +35640,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35625,7 +35689,7 @@
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35750,7 +35814,7 @@
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -35874,7 +35938,7 @@
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -35944,7 +36008,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -35993,7 +36057,7 @@
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
@@ -36068,7 +36132,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36112,17 +36176,17 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -36370,7 +36434,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -36440,7 +36504,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q292" s="2" t="inlineStr">
@@ -36484,17 +36548,17 @@
       </c>
       <c r="AB292" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC292" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -36932,7 +36996,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -36976,17 +37040,17 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -37106,7 +37170,7 @@
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -37230,7 +37294,7 @@
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -37354,7 +37418,7 @@
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -37397,12 +37461,12 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr"/>
@@ -37424,7 +37488,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37473,12 +37537,12 @@
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -37521,12 +37585,12 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
@@ -37548,7 +37612,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37597,7 +37661,7 @@
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
@@ -37645,12 +37709,12 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
@@ -37672,7 +37736,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37721,7 +37785,7 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
@@ -37759,32 +37823,36 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N303" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37792,7 +37860,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37816,17 +37884,17 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA303" s="2" t="inlineStr">
@@ -37836,17 +37904,17 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -37879,32 +37947,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -37912,7 +37984,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37936,17 +38008,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -37956,17 +38028,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -37999,32 +38071,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -38032,7 +38108,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38056,17 +38132,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38076,17 +38152,17 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -38152,7 +38228,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38201,12 +38277,12 @@
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -38272,7 +38348,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38321,7 +38397,7 @@
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
@@ -38392,7 +38468,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38436,17 +38512,17 @@
       </c>
       <c r="AB308" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
